--- a/target/test-classes/Output.xlsx
+++ b/target/test-classes/Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
@@ -38,25 +38,16 @@
     <t>Junior Account Assistant</t>
   </si>
   <si>
-    <t>Srinu Madaka</t>
+    <t>sgdfg fdhgfh</t>
   </si>
   <si>
-    <t>(Deleted)</t>
+    <t>yedghjb1 ru84 90jsnd</t>
   </si>
   <si>
-    <t>2026-02-02</t>
+    <t>10-02-2026</t>
   </si>
   <si>
     <t>Application Initiated</t>
-  </si>
-  <si>
-    <t>Indu Neeladhri</t>
-  </si>
-  <si>
-    <t>Barnbas Telagareddy</t>
-  </si>
-  <si>
-    <t>Harika Vanum</t>
   </si>
 </sst>
 </file>
@@ -101,14 +92,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="2.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="0.9296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.50390625" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="17.72265625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="13.375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.88671875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="18.25" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="16.35546875" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="17.19140625" customWidth="true" bestFit="true"/>
   </cols>
@@ -162,84 +153,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
